--- a/MarketBullets_Master_Chart_Index.xlsx
+++ b/MarketBullets_Master_Chart_Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a1efcf13b2cc8d9a/Documents/GitHub/WEBSITECHARTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9017183-3BDB-4F6B-9522-03A090B4EB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{561CB34D-6201-43FF-BF1B-1FDB92941336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0F0C2862-E87D-48A6-B1CD-4F9C66413518}"/>
   </bookViews>
@@ -1929,6 +1929,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2140DC-1C2A-4E7F-919D-477AA469560B}">
   <dimension ref="A1:J84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="31" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
